--- a/光伏配储项目/电价数据/2026/海丰站.xlsx
+++ b/光伏配储项目/电价数据/2026/海丰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.6123999999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8201499999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6890700000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60739</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6021299999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43185</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5170399999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19721</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.21807</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.2128</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17297</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19846</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06189</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24229</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24076</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23002</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.23106</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.89273</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22124</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.53088</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5320199999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6117899999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.62003</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72621</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.23227</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6545700000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.94951</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5547300000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.29115</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41631</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.1584</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.27411</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.36567</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.5417</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.52899</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7693300000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.82129</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.33088</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.13088</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86556</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79362</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5145299999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70041</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74517</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8626200000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9035</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48919</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50719</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49683</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49702</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47966</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7021000000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55975</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66096</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43315</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42896</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.57985</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85477</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07032</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58201</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.9351900000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.88934</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.55845</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.83824</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.24542</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05691</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50169</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58557</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54495</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53801</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86214</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6056900000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7768400000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8562000000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.22379</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15934</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.88647</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1782</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.33685</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.11832</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.16291</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.72161</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.05383</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89378</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.06721</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.98287</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.08453</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.88797</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8133400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44634</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48268</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48021</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46731</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.19217</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16079</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.5400700000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48423</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.57136</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.5786699999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6621900000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.62766</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8972599999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.58285</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.69856</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7769299999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8640599999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52262</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7781699999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7174199999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6443300000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63561</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.58163</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45618</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50296</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57726</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61099</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5788099999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.60033</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23477</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6101799999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.75487</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57769</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.72919</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47064</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.60594</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.46812</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.56314</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60145</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7355900000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.70388</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5778799999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51379</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6456799999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45418</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34162</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51401</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49138</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44576</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.47956</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.64771</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.50119</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.49737</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11749</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59211</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49022</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49938</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6795599999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53313</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.67296</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.53086</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.7397699999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.57267</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50196</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.49212</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30966</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24347</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26474</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14604</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.06105</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.24659</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18503</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24577</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26295</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22344</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08517</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.17958</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14206</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01437</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26434</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33045</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24688</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21365</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09962</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24355</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10342</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04397</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20923</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05077</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19509</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.04783</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06159000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32348</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30107</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78495</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87151</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.73673</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.60222</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44876</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50395</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56043</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6529400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8694400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46082</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.69843</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45495</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83417</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5772999999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5223099999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3353</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9050199999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23631</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24429</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26859</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40737</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8117300000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3842</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08471</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.74253</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.60684</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46791</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23037</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.06367</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24461</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02896</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.67032</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27395</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23681</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23946</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21525</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25698</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27424</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20696</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20745</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.09695000000000001</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.2259</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09806000000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20431</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23715</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24039</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.25645</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22402</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27003</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24742</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.24236</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24754</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22943</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26635</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24379</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30764</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27832</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.46552</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32671</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.23341</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.48664</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.76034</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.45583</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.56914</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.54892</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.51766</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5845</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.45908</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.69397</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.48339</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5368999999999999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.87258</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.61697</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.49018</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.57768</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5388200000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.5247200000000001</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.71023</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.53015</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5420199999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.5609500000000001</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.49466</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.59641</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.47064</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.71921</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.5283600000000001</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5398099999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.48449</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.76273</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.46772</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.47261</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49092</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2243</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.17404</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24987</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24486</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24732</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24459</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.22058</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24432</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25967</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23794</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22664</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26541</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33121</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6402</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.90377</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31522</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.52428</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.48617</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5228400000000001</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6963400000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.60084</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.7110599999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.66859</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7563</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.85851</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46471</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.73193</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.64879</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.55453</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5707100000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.49173</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33196</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47783</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.51664</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6325499999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.69399</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8839600000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.4681</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.5188400000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.52616</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.50858</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.46278</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75506</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60714</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6541</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.14416</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.58997</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.35255</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4711</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47286</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.50104</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.23907</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27241</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26567</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23773</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.13456</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.13355</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23776</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25644</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23671</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.12718</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22394</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.23006</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.12314</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.12261</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.25202</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.09879</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11679</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24805</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18997</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01705</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25326</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25554</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24757</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25689</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23258</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.23154</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27212</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15389</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23431</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.11105</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13882</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.10486</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.11324</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.11144</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.11144</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.11252</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23873</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.10279</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.11144</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.11161</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22789</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10493</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10483</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11597</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07479999999999999</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11808</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00253</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14174</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01598</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.0008900000000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03846</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02217</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03636</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19978</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30041</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.53415</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.47839</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.21617</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24064</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23712</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11836</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23282</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12185</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08529</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.10288</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.11255</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.12721</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.09245</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.13794</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.15743</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5704600000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86791</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8585199999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10824</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.10321</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.15564</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.11111</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47335</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.10154</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6643300000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.56372</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.60348</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.08463</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9742999999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.57224</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72788</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.6183999999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8305900000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8288099999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83309</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9308099999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5612999999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6144299999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33505</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.44231</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48248</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26625</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.26059</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.24012</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.23281</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11959</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24878</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25684</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.56872</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32258</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70882</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.55752</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47215</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.78554</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.85888</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.50117</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58616</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.11375</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.89747</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.55583</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64898</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49156</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4674700000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.47666</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22373</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3406</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43632</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50446</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.60002</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.33253</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.08613</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.65203</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.9124500000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52642</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6647999999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.58227</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45784</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.81909</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74903</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.99339</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8961699999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.80736</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72604</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.43107</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.50715</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.46575</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.51434</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.85224</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.5139600000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.22262</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.63029</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.86597</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.5309199999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.50606</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5520900000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.69626</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.68679</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.44321</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.51125</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35094</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.91932</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5277999999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49727</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.51693</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.49621</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5251399999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.61133</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.50185</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.47592</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.47303</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45978</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35177</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17582</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04571</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12091</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22502</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14756</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14402</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19212</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15181</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15403</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19586</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14058</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.57208</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37901</v>
       </c>
     </row>
   </sheetData>
